--- a/docs/phase2/ITC327W_Phase2_Project_Progress_Tracker-1.xlsx
+++ b/docs/phase2/ITC327W_Phase2_Project_Progress_Tracker-1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tshep\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tshep\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FD49CD-5197-4630-999B-618D866AE7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7138CB-6427-4E89-BD01-2A41AD0871DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="230">
   <si>
     <t>ITC327W Phase 2 Project Progress Tracker</t>
   </si>
@@ -621,21 +621,6 @@
     <t>Updated Project Tracker</t>
   </si>
   <si>
-    <t>https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram%20-%20Overtime.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload</t>
-  </si>
-  <si>
-    <t>https://canva.link/4iw7qdaph3idtkh</t>
-  </si>
-  <si>
-    <t>https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload</t>
-  </si>
-  <si>
-    <t>https://lucid.app/lucidchart/bd59e6f9-8f1d-4421-8316-84cc445b37c5/edit?viewport_loc=-597%2C-24%2C3975%2C1710%2C0_0&amp;invitationId=inv_1cb79b5c-175b-4651-a1bd-d4d0ac932d90</t>
-  </si>
-  <si>
-    <t>https://www.figma.com/make/ksSuk3HNqtRmwr8my3Dw7E/Sebenza-Clocking-System?t=NoVGadtCKHc67q7K-1</t>
-  </si>
-  <si>
     <t>Kwanele &amp; Paki</t>
   </si>
   <si>
@@ -678,9 +663,6 @@
     <t xml:space="preserve">Nkosinathi will follow up and gather the feedback atleast a week before we need to submit so that we can have enough time to look at the document in its final form fix what needs to be fixed and submit a well thought document </t>
   </si>
   <si>
-    <t xml:space="preserve">14 September 2026 - 12 October 2026	</t>
-  </si>
-  <si>
     <t>Finish the SRS, keep the GitHub repository and Microsoft Project file current, and prepare for the Phase 2 presentation.</t>
   </si>
   <si>
@@ -691,24 +673,6 @@
   </si>
   <si>
     <t>Ensuring that our diagrams explain what our system does properly</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>The most challenging activities were separating tasks efficiently and coordinating work when some members found particular tasks difficult. The group discussed the difficulties, used members' strengths and allowed compromises or task swaps so that the required work could be completed.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve">					
-					</t>
-    </r>
   </si>
   <si>
     <r>
@@ -742,9 +706,6 @@
     <t>We gave each technology a clear responsibility: Flutter for the employee mobile interface, ASP.NET for the management web application and business logic, and Supabase for shared authentication and data storage. We then aligned the architecture, UML, ERD and interfaces so that they all represented the same requirements, data and processes.</t>
   </si>
   <si>
-    <t>We have succesfuly separated tasks among each other , the wireframes have been finished, the system archetecture, use case and sequence diagrams are completed. The SRS document is being updated and getting ready for phase 2 information.</t>
-  </si>
-  <si>
     <t xml:space="preserve">NONE </t>
   </si>
   <si>
@@ -752,13 +713,61 @@
   </si>
   <si>
     <t>14 September 2026 - 13 October 2026</t>
+  </si>
+  <si>
+    <t>We have succesfuly separated tasks among each other , the wireframes have been finished, the system archetecture, use case and sequence diagrams and ERD are completed. The SRS document is Up to date.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">The most challenging Activity was getting the use case right. Also making sure that our wireframes include everything that was required.	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">				
+					</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">14 September 2026 - 13 October 2026	</t>
+  </si>
+  <si>
+    <t>https://github.com/biyasekwanele/sebenza-clocking-system.git</t>
+  </si>
+  <si>
+    <t>https://www.figma.com/make/ksSuk3HNqtRmwr8my3Dw7E/Sebenza-Clocking-System?code-node-id=0-6&amp;p=f&amp;fullscreen=1</t>
+  </si>
+  <si>
+    <t>https://lucid.app/lucidchart/bd59e6f9-8f1d-4421-8316-84cc445b37c5/edit?viewport_loc=-662%2C-448%2C5038%2C2106%2C0_0&amp;invitationId=inv_1cb79b5c-175b-4651-a1bd-d4d0ac932d90</t>
+  </si>
+  <si>
+    <t>https://github.com/biyasekwanele//sebenza-clocking-system.git</t>
+  </si>
+  <si>
+    <t>https://app.diagrams.net/#G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D</t>
+  </si>
+  <si>
+    <t>https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram-Overtime.drawio&amp;dark=auto#R%3Cmxfile%3E%3Cdiagram%20name%3D%22Page-1%22%20id%3D%22l3LJjRWJDzVEaLW4UUNY%22%3E7Zxbc5s4FIB%2FjWfSh2S4gx99S5tttsnGabrbl44Msk2DEQFhx%2Fn1KyGBuSVEtfHaXaczKRykI6FzPh1dUDrqYPH8MQTB%2FE%2FkQK%2BjSM5zRx12FEWRNI38RyVrJjEsiQlmoeswkbwRjN0XyIWpNHYdGBUSYoQ87AZFoY18H9q4IANhiFbFZFPkFUsNwAxWBGMbeFXpN9fBcya1FHMj%2FwTd2TwtWTa67MkE2I%2BzEMU%2BL8%2Bjic4dED6edRR1qI%2BsIWmaAbmWFfrvA8u2AGkZvJ2iOXDQKidSRx11ECKE2dXieQA92uZpc7J8l688zd4nhD5%2BT4bLu5up%2F2TCl7XiSOOnq6X%2B9eHcrGrhiiO8TpuO1Dygl%2FHCu3an0HN9ctcPYOguIIYheeJx8e1G1l%2FNXQzHAbBp1hVxKiKb44VH7mRySeyMAckS8nsnRME9CGeQVkNKEngeCCJ3klSDSkJox2HkLuEdjJh%2FUSmKMS16kPkNFQYoxEQS4ZCUQYUQRHgFI3LZ9%2BFq5BDfSF%2FQ7HcU4ymmdujD7EEm6qi9zU0En2Lo23BUk476QHrjuROwRK5zR2rn%2BrOCNqmQkrzSEjpvJEhcr5LCHNK3BCF2bTcAySsS8%2FRsjGjbk%2FdGj5mfK7RCYAK9fubKA%2BTRhEMfJbacup6XiogjS11d1%2FuZntyTfm9gDVWag5gvJx8lP7naMqPyu5xbJGLmYUvgxdzDuACGGD7nvJA78keISO5wTZLMc4gaqsXyrTY8p7DxTkrVuWrAe49ZpmpDCrngsAiAY53AOWJwxP29StRrBLxN2q%2Fx0RvfXnwZ3RPhNzghv3tBsDNkZIkzk4b6MkOa1RJD3RNDJ4b2xtA4DsAERJDiE5MatMWPpmt7ikGydALoBNDeALpFEZ6FcPzXdWvsGKa8L3Z4QdRlXp1QpTChOLRh8ywqB10OFdpMLpmH9sjE0SeyCcIYLai3%2Bk6PTmypzEP2Y8GB1WHVWauOyVljTsgxK9j2bT%2BoeJrU14ZGr%2BRXDpyC2MOZS%2BCU84axcWF8byQKyNjFmDFNTEDLKbRcigl9cM76CQKwJCvBM8uW8coU3QTQJ89vklZe0M79Di5duEpXBHg5xEdYUcXiiThXpToPDqEHMOm0Cg6R8%2BB0FaTOQRNtxMRgnUsQINKlRbnCbqlgg4BsqheKXqBA06SSvzOl9QpMszZzVgHmzTxTfr2gXBG9QRHzg4qiBMesBbcgVNkhodbBEio6VW%2BJ2e4emX0AnusATGGNYBS5iBIMfIfihrwjZFa1uhVmDUWAWcWszy0Mrao3KGobWnWH0Ha3hRbR4EAGpyCaZ7yRx3xx2vofBNytWa30Agm8ZIjLSJUSpRKZW8Fw6Uak%2BrWUvgL0u%2BFtldSuLkBqBTCeW5jUCvJlRW2TapzC6%2F4ITafqe4mv49H1aEAXC0n35yTzVwll42MDLOhc3p9EwVtoHmys1aXK%2BFhXLJFYaxm1uYUJNuQGRW0TbAoQfEwx9ECY3WdUva0hVfLcCB94PDVMq8iAKTLsNeX63OIoqg2K2kbR2geKv9cq0V5D4teATzhTvM4iDHAcJWu1hBG6ZASdH5N1SQDwh%2BMLkZplXJRGl6akiYRIQ6vNLc6lYr6tqGUu09Y%2BhcjjX%2BllCNNFos1ibxtk7g7DrlrBUBMZqZbDo1neif%2FV8FhR1DaGIku5JwyFMTT3iOF4jlbVsekO%2BeM%2BK11IkmI0ILnx9DQJmk4jWHBi4Q0YXStjm8703hs9zdrc4jswVoOitrHVBLBtfYnohPce8V6yLRq2NQOJBcJWYT%2BntGulseHWAVhRi18TWJbIPmoZY0szd4NxRdHuMH6R51cP8cMTmN4Afx19%2F7ReXZ6LUHyi8xjojLOhcDqLPeiBsFKaBXa1bcJpmntrDiuKWuZQ32E0PX1x9J%2FNQ8fxZOFSFQ60Xf7xwlkvCEJE%2BCHVgz%2Fph4z0I2qSRbLRYkGse4SrSLJe3N4wDJHoKStybW7xfVKpQVHL1Iqs7DZRmy55nsLsgSMOko96JRA7Lv7hodmBB9js24E0svHPcN6Hqi51a3MLo6opDYpaRrW7Q1RPXzQc0vbN1Zfx6O4%2BT%2BQZPf%2Bblq4MfLhK744w1Jb5tWSR3ZrsI%2FlSbnF%2B1QZFLfMrfJ7lMgQL6uINh1WS5ofhaAmpFRhT2x6%2B0Bu52%2B0JWeBhLhM7daFK1VMXplVafVGKds829bc5dfH5%2BzP%2B5%2Frpxx%2F258m38fzn%2BiX6%2B1x9j4HJ6%2BGiAevsWzRUzTlmLgK8j7ahz042lTvvhes4SU%2B8MYxUZ4HXvoSUhtk8oL6D%2BQWbVUxWOWSm7cli2u9ksZGXHP%2B78pfMdO3ZKz2EUW8uS9GFzUVuN38rgvW4mz%2FUoY7%2BBQ%3D%3D%3C%2Fdiagram%3E%3C%2Fmxfile%3E</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12zlE3PpSnzZ9_Acj_QPFFUC4bUvSOJeX/view?usp=sharing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -787,6 +796,12 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="5"/>
       <color theme="10"/>
       <name val="Carlito"/>
     </font>
@@ -847,7 +862,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -910,6 +925,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1442,11 +1460,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15">
+    <row r="8" spans="1:8" ht="28.5">
       <c r="A8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="11" t="s">
+        <v>223</v>
+      </c>
       <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
@@ -1459,7 +1479,7 @@
         <v>41</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15">
@@ -1526,6 +1546,9 @@
       <formula1>"Not Started,In Progress,Completed,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{7A5DEE27-E5E7-4EA4-A3C4-CAD2C70B22D1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1620,7 +1643,7 @@
       </c>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10" ht="28.5">
+    <row r="5" spans="1:10" ht="57">
       <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
@@ -1646,11 +1669,11 @@
         <v>1</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="99.75">
+    <row r="6" spans="1:10" ht="42.75">
       <c r="A6" s="2" t="s">
         <v>63</v>
       </c>
@@ -1676,11 +1699,11 @@
         <v>1</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="128.25">
+    <row r="7" spans="1:10" ht="379.5">
       <c r="A7" s="2" t="s">
         <v>66</v>
       </c>
@@ -1705,8 +1728,8 @@
       <c r="H7" s="8">
         <v>1</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>193</v>
+      <c r="I7" s="24" t="s">
+        <v>228</v>
       </c>
       <c r="J7" s="5"/>
     </row>
@@ -1721,7 +1744,7 @@
         <v>71</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E8" s="10">
         <v>46288</v>
@@ -1736,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="J8" s="5"/>
     </row>
@@ -1766,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="J9" s="5"/>
     </row>
@@ -1796,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="J10" s="5"/>
     </row>
@@ -1811,10 +1834,10 @@
         <v>80</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E11" s="10">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>34</v>
@@ -1826,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="J11" s="5"/>
     </row>
@@ -1844,7 +1867,7 @@
         <v>160</v>
       </c>
       <c r="E12" s="10">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>34</v>
@@ -1874,7 +1897,7 @@
         <v>161</v>
       </c>
       <c r="E13" s="10">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>34</v>
@@ -1904,7 +1927,7 @@
         <v>162</v>
       </c>
       <c r="E14" s="10">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>34</v>
@@ -1915,7 +1938,9 @@
       <c r="H14" s="8">
         <v>1</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="11" t="s">
+        <v>226</v>
+      </c>
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10">
@@ -1932,7 +1957,7 @@
         <v>162</v>
       </c>
       <c r="E15" s="10">
-        <v>46300</v>
+        <v>46278</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>34</v>
@@ -2203,11 +2228,13 @@
   <hyperlinks>
     <hyperlink ref="I9" r:id="rId1" xr:uid="{2E6107C7-A3DE-448D-8CFB-FAA6D2A490C2}"/>
     <hyperlink ref="I4" r:id="rId2" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1rESYHt5o1iQarVEFVaAx0mJylvMq4XkD%26export%3Ddownload" xr:uid="{2C1AB1D1-B0F7-4D0D-B352-46BFD02BC847}"/>
-    <hyperlink ref="I6" r:id="rId3" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload" xr:uid="{355BCCA4-7894-4A1D-B30C-EAF1DCC0DE32}"/>
-    <hyperlink ref="I7" r:id="rId4" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{9F80DF1F-1A11-48B5-A1D0-BD96E738EA50}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{355BCCA4-7894-4A1D-B30C-EAF1DCC0DE32}"/>
+    <hyperlink ref="I7" r:id="rId4" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" display="https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram%20-%20Overtime.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{9F80DF1F-1A11-48B5-A1D0-BD96E738EA50}"/>
     <hyperlink ref="I8" r:id="rId5" xr:uid="{06C77801-245F-4264-B312-4FFF247E03F5}"/>
     <hyperlink ref="I10" r:id="rId6" xr:uid="{EDADBB19-03AA-410A-A2EE-55A59051E615}"/>
     <hyperlink ref="I11" r:id="rId7" xr:uid="{9830CD24-744C-46E4-9E52-D326D6F64D32}"/>
+    <hyperlink ref="I14" r:id="rId8" xr:uid="{7D70AB5A-823D-49FD-A296-FEDB537D1C71}"/>
+    <hyperlink ref="I5" r:id="rId9" location="G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D" xr:uid="{26ADDA44-418D-4A9A-BE8E-A78689694655}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2349,10 +2376,10 @@
         <v>169</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F5" s="10">
         <v>46283</v>
@@ -2374,7 +2401,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="42.75">
+    <row r="6" spans="1:12" ht="57">
       <c r="A6" s="5" t="s">
         <v>172</v>
       </c>
@@ -2397,7 +2424,7 @@
         <v>170</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>168</v>
@@ -2433,7 +2460,7 @@
         <v>170</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>168</v>
@@ -2446,7 +2473,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="99.75">
+    <row r="8" spans="1:12" ht="57">
       <c r="A8" s="5" t="s">
         <v>156</v>
       </c>
@@ -2469,7 +2496,7 @@
         <v>180</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>168</v>
@@ -2482,7 +2509,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="128.25">
+    <row r="9" spans="1:12" ht="379.5">
       <c r="A9" s="5" t="s">
         <v>157</v>
       </c>
@@ -2504,8 +2531,8 @@
       <c r="G9" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>193</v>
+      <c r="H9" s="24" t="s">
+        <v>228</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>168</v>
@@ -2541,7 +2568,7 @@
         <v>186</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>168</v>
@@ -2577,7 +2604,7 @@
         <v>186</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>168</v>
@@ -2601,10 +2628,10 @@
         <v>178</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F12" s="10">
         <v>46287</v>
@@ -2613,7 +2640,7 @@
         <v>189</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>168</v>
@@ -2643,10 +2670,10 @@
         <v>190</v>
       </c>
       <c r="F13" s="10">
-        <v>46297</v>
+        <v>46308</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>192</v>
@@ -3220,11 +3247,11 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H9" r:id="rId1" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{B5CA926F-E857-47A9-871C-FC293A7D2038}"/>
+    <hyperlink ref="H9" r:id="rId1" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" display="https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram%20-%20Overtime.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{B5CA926F-E857-47A9-871C-FC293A7D2038}"/>
     <hyperlink ref="H5" r:id="rId2" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1rESYHt5o1iQarVEFVaAx0mJylvMq4XkD%26export%3Ddownload" xr:uid="{E7DC9E2A-B1B2-4857-A0D4-98129109304F}"/>
-    <hyperlink ref="H6" r:id="rId3" xr:uid="{E019AB39-1D4E-467F-8F27-98AF09926AC2}"/>
-    <hyperlink ref="H7" r:id="rId4" xr:uid="{69B67A7E-F5DF-4731-9108-D2B26EA17B5F}"/>
-    <hyperlink ref="H8" r:id="rId5" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload" xr:uid="{DBC01AE3-04B8-416B-9595-44BE25A3933E}"/>
+    <hyperlink ref="H6" r:id="rId3" location="G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D" xr:uid="{E019AB39-1D4E-467F-8F27-98AF09926AC2}"/>
+    <hyperlink ref="H7" r:id="rId4" location="G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D" xr:uid="{69B67A7E-F5DF-4731-9108-D2B26EA17B5F}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{DBC01AE3-04B8-416B-9595-44BE25A3933E}"/>
     <hyperlink ref="H10" r:id="rId6" xr:uid="{7487445C-39DC-478E-A0C1-51E26435126C}"/>
     <hyperlink ref="H11" r:id="rId7" xr:uid="{6CCC7B2B-D020-47F7-8043-90FE30930310}"/>
     <hyperlink ref="H12" r:id="rId8" xr:uid="{69D4528E-61E1-4387-8E6E-26DBAC7C4506}"/>
@@ -3291,7 +3318,7 @@
         <v>58</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>171</v>
@@ -3310,15 +3337,15 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="57">
       <c r="A5" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>168</v>
@@ -3334,15 +3361,15 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" ht="85.5">
+    <row r="6" spans="1:8" ht="28.5">
       <c r="A6" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>168</v>
@@ -3358,15 +3385,15 @@
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="99.75">
+    <row r="7" spans="1:8" ht="297">
       <c r="A7" t="s">
         <v>67</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>193</v>
+        <v>209</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>228</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>168</v>
@@ -3387,10 +3414,10 @@
         <v>70</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>168</v>
@@ -3399,7 +3426,7 @@
         <v>46288</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>168</v>
@@ -3411,10 +3438,10 @@
         <v>73</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>168</v>
@@ -3435,10 +3462,10 @@
         <v>76</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>168</v>
@@ -3459,10 +3486,10 @@
         <v>115</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>168</v>
@@ -3489,9 +3516,9 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1rESYHt5o1iQarVEFVaAx0mJylvMq4XkD%26export%3Ddownload" xr:uid="{BC28DF17-63E6-47BC-BA78-B6935EDD0CDA}"/>
-    <hyperlink ref="C5" r:id="rId2" xr:uid="{9F01BBAD-8F77-45FC-9D84-2003B71C6FD4}"/>
-    <hyperlink ref="C6" r:id="rId3" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload" xr:uid="{2AF1EAE9-F8D1-49EF-AF7D-566C521146B1}"/>
-    <hyperlink ref="C7" r:id="rId4" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{AE6E4056-F5FA-416E-B7C3-AA75D0E1F713}"/>
+    <hyperlink ref="C5" r:id="rId2" location="G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D" xr:uid="{9F01BBAD-8F77-45FC-9D84-2003B71C6FD4}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{2AF1EAE9-F8D1-49EF-AF7D-566C521146B1}"/>
+    <hyperlink ref="C7" r:id="rId4" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" display="https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram%20-%20Overtime.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{AE6E4056-F5FA-416E-B7C3-AA75D0E1F713}"/>
     <hyperlink ref="C8" r:id="rId5" xr:uid="{DBB043FB-01CA-4628-BB08-82C86E442EF8}"/>
     <hyperlink ref="C9" r:id="rId6" xr:uid="{82B08C55-5769-410C-8DEB-7239FC87F6D9}"/>
     <hyperlink ref="C10" r:id="rId7" xr:uid="{1556F12A-BF1A-4FAC-98A4-EE50F9FF4D7D}"/>
@@ -3562,13 +3589,13 @@
         <v>46279</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>162</v>
@@ -3589,13 +3616,13 @@
         <v>46272</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>159</v>
@@ -4005,7 +4032,7 @@
     <col min="2" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1">
@@ -4023,7 +4050,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C3" s="17"/>
       <c r="E3" s="1" t="s">
@@ -4053,7 +4080,7 @@
         <v>126</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C5" s="18"/>
       <c r="E5" t="s">
@@ -4068,7 +4095,7 @@
         <v>128</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C6" s="17"/>
       <c r="E6" t="s">
@@ -4083,7 +4110,7 @@
         <v>130</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C7" s="17"/>
       <c r="E7" t="s">
@@ -4098,7 +4125,7 @@
         <v>132</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C8" s="17"/>
       <c r="E8" t="s">
@@ -4128,7 +4155,7 @@
         <v>136</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C10" s="17"/>
       <c r="E10" t="s">
@@ -4143,7 +4170,7 @@
         <v>138</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C11" s="17"/>
       <c r="E11" t="s">
@@ -4249,7 +4276,7 @@
     </row>
     <row r="4" spans="1:6" ht="38.1" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -4285,7 +4312,7 @@
     </row>
     <row r="8" spans="1:6" ht="38.1" customHeight="1">
       <c r="A8" s="22" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -4321,7 +4348,7 @@
     </row>
     <row r="12" spans="1:6" ht="38.1" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -4349,7 +4376,7 @@
     </row>
     <row r="16" spans="1:6" ht="38.1" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -4377,7 +4404,7 @@
     </row>
     <row r="20" spans="1:6" ht="38.1" customHeight="1">
       <c r="A20" s="17" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -4405,7 +4432,7 @@
     </row>
     <row r="24" spans="1:6" ht="38.1" customHeight="1">
       <c r="A24" s="17" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>

--- a/docs/phase2/ITC327W_Phase2_Project_Progress_Tracker-1.xlsx
+++ b/docs/phase2/ITC327W_Phase2_Project_Progress_Tracker-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tshep\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7138CB-6427-4E89-BD01-2A41AD0871DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABAD999-CBEB-4C63-8B1E-4D5659EE45C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -760,7 +760,7 @@
     <t>https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram-Overtime.drawio&amp;dark=auto#R%3Cmxfile%3E%3Cdiagram%20name%3D%22Page-1%22%20id%3D%22l3LJjRWJDzVEaLW4UUNY%22%3E7Zxbc5s4FIB%2FjWfSh2S4gx99S5tttsnGabrbl44Msk2DEQFhx%2Fn1KyGBuSVEtfHaXaczKRykI6FzPh1dUDrqYPH8MQTB%2FE%2FkQK%2BjSM5zRx12FEWRNI38RyVrJjEsiQlmoeswkbwRjN0XyIWpNHYdGBUSYoQ87AZFoY18H9q4IANhiFbFZFPkFUsNwAxWBGMbeFXpN9fBcya1FHMj%2FwTd2TwtWTa67MkE2I%2BzEMU%2BL8%2Bjic4dED6edRR1qI%2BsIWmaAbmWFfrvA8u2AGkZvJ2iOXDQKidSRx11ECKE2dXieQA92uZpc7J8l688zd4nhD5%2BT4bLu5up%2F2TCl7XiSOOnq6X%2B9eHcrGrhiiO8TpuO1Dygl%2FHCu3an0HN9ctcPYOguIIYheeJx8e1G1l%2FNXQzHAbBp1hVxKiKb44VH7mRySeyMAckS8nsnRME9CGeQVkNKEngeCCJ3klSDSkJox2HkLuEdjJh%2FUSmKMS16kPkNFQYoxEQS4ZCUQYUQRHgFI3LZ9%2BFq5BDfSF%2FQ7HcU4ymmdujD7EEm6qi9zU0En2Lo23BUk476QHrjuROwRK5zR2rn%2BrOCNqmQkrzSEjpvJEhcr5LCHNK3BCF2bTcAySsS8%2FRsjGjbk%2FdGj5mfK7RCYAK9fubKA%2BTRhEMfJbacup6XiogjS11d1%2FuZntyTfm9gDVWag5gvJx8lP7naMqPyu5xbJGLmYUvgxdzDuACGGD7nvJA78keISO5wTZLMc4gaqsXyrTY8p7DxTkrVuWrAe49ZpmpDCrngsAiAY53AOWJwxP29StRrBLxN2q%2Fx0RvfXnwZ3RPhNzghv3tBsDNkZIkzk4b6MkOa1RJD3RNDJ4b2xtA4DsAERJDiE5MatMWPpmt7ikGydALoBNDeALpFEZ6FcPzXdWvsGKa8L3Z4QdRlXp1QpTChOLRh8ywqB10OFdpMLpmH9sjE0SeyCcIYLai3%2Bk6PTmypzEP2Y8GB1WHVWauOyVljTsgxK9j2bT%2BoeJrU14ZGr%2BRXDpyC2MOZS%2BCU84axcWF8byQKyNjFmDFNTEDLKbRcigl9cM76CQKwJCvBM8uW8coU3QTQJ89vklZe0M79Di5duEpXBHg5xEdYUcXiiThXpToPDqEHMOm0Cg6R8%2BB0FaTOQRNtxMRgnUsQINKlRbnCbqlgg4BsqheKXqBA06SSvzOl9QpMszZzVgHmzTxTfr2gXBG9QRHzg4qiBMesBbcgVNkhodbBEio6VW%2BJ2e4emX0AnusATGGNYBS5iBIMfIfihrwjZFa1uhVmDUWAWcWszy0Mrao3KGobWnWH0Ha3hRbR4EAGpyCaZ7yRx3xx2vofBNytWa30Agm8ZIjLSJUSpRKZW8Fw6Uak%2BrWUvgL0u%2BFtldSuLkBqBTCeW5jUCvJlRW2TapzC6%2F4ITafqe4mv49H1aEAXC0n35yTzVwll42MDLOhc3p9EwVtoHmys1aXK%2BFhXLJFYaxm1uYUJNuQGRW0TbAoQfEwx9ECY3WdUva0hVfLcCB94PDVMq8iAKTLsNeX63OIoqg2K2kbR2geKv9cq0V5D4teATzhTvM4iDHAcJWu1hBG6ZASdH5N1SQDwh%2BMLkZplXJRGl6akiYRIQ6vNLc6lYr6tqGUu09Y%2BhcjjX%2BllCNNFos1ibxtk7g7DrlrBUBMZqZbDo1neif%2FV8FhR1DaGIku5JwyFMTT3iOF4jlbVsekO%2BeM%2BK11IkmI0ILnx9DQJmk4jWHBi4Q0YXStjm8703hs9zdrc4jswVoOitrHVBLBtfYnohPce8V6yLRq2NQOJBcJWYT%2BntGulseHWAVhRi18TWJbIPmoZY0szd4NxRdHuMH6R51cP8cMTmN4Afx19%2F7ReXZ6LUHyi8xjojLOhcDqLPeiBsFKaBXa1bcJpmntrDiuKWuZQ32E0PX1x9J%2FNQ8fxZOFSFQ60Xf7xwlkvCEJE%2BCHVgz%2Fph4z0I2qSRbLRYkGse4SrSLJe3N4wDJHoKStybW7xfVKpQVHL1Iqs7DZRmy55nsLsgSMOko96JRA7Lv7hodmBB9js24E0svHPcN6Hqi51a3MLo6opDYpaRrW7Q1RPXzQc0vbN1Zfx6O4%2BT%2BQZPf%2Bblq4MfLhK744w1Jb5tWSR3ZrsI%2FlSbnF%2B1QZFLfMrfJ7lMgQL6uINh1WS5ofhaAmpFRhT2x6%2B0Bu52%2B0JWeBhLhM7daFK1VMXplVafVGKds829bc5dfH5%2BzP%2B5%2Frpxx%2F258m38fzn%2BiX6%2B1x9j4HJ6%2BGiAevsWzRUzTlmLgK8j7ahz042lTvvhes4SU%2B8MYxUZ4HXvoSUhtk8oL6D%2BQWbVUxWOWSm7cli2u9ksZGXHP%2B78pfMdO3ZKz2EUW8uS9GFzUVuN38rgvW4mz%2FUoY7%2BBQ%3D%3D%3C%2Fdiagram%3E%3C%2Fmxfile%3E</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/12zlE3PpSnzZ9_Acj_QPFFUC4bUvSOJeX/view?usp=sharing</t>
+    <t>https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload</t>
   </si>
 </sst>
 </file>
@@ -895,18 +895,21 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -917,19 +920,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1192,24 +1192,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" ht="33.950000000000003" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1300,56 +1300,56 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1376,16 +1376,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="4" t="s">
@@ -1394,13 +1394,13 @@
       <c r="B3" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="4" t="s">
@@ -1489,50 +1489,50 @@
       <c r="B10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1568,18 +1568,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="42.75">
+    <row r="6" spans="1:10" ht="99.75">
       <c r="A6" s="2" t="s">
         <v>63</v>
       </c>
@@ -1728,7 +1728,7 @@
       <c r="H7" s="8">
         <v>1</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="12" t="s">
         <v>228</v>
       </c>
       <c r="J7" s="5"/>
@@ -2228,7 +2228,7 @@
   <hyperlinks>
     <hyperlink ref="I9" r:id="rId1" xr:uid="{2E6107C7-A3DE-448D-8CFB-FAA6D2A490C2}"/>
     <hyperlink ref="I4" r:id="rId2" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1rESYHt5o1iQarVEFVaAx0mJylvMq4XkD%26export%3Ddownload" xr:uid="{2C1AB1D1-B0F7-4D0D-B352-46BFD02BC847}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{355BCCA4-7894-4A1D-B30C-EAF1DCC0DE32}"/>
+    <hyperlink ref="I6" r:id="rId3" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload" xr:uid="{355BCCA4-7894-4A1D-B30C-EAF1DCC0DE32}"/>
     <hyperlink ref="I7" r:id="rId4" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" display="https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram%20-%20Overtime.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{9F80DF1F-1A11-48B5-A1D0-BD96E738EA50}"/>
     <hyperlink ref="I8" r:id="rId5" xr:uid="{06C77801-245F-4264-B312-4FFF247E03F5}"/>
     <hyperlink ref="I10" r:id="rId6" xr:uid="{EDADBB19-03AA-410A-A2EE-55A59051E615}"/>
@@ -2276,20 +2276,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -2473,7 +2473,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="57">
+    <row r="8" spans="1:12" ht="99.75">
       <c r="A8" s="5" t="s">
         <v>156</v>
       </c>
@@ -2531,7 +2531,7 @@
       <c r="G9" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="12" t="s">
         <v>228</v>
       </c>
       <c r="I9" s="5" t="s">
@@ -3251,7 +3251,7 @@
     <hyperlink ref="H5" r:id="rId2" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1rESYHt5o1iQarVEFVaAx0mJylvMq4XkD%26export%3Ddownload" xr:uid="{E7DC9E2A-B1B2-4857-A0D4-98129109304F}"/>
     <hyperlink ref="H6" r:id="rId3" location="G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D" xr:uid="{E019AB39-1D4E-467F-8F27-98AF09926AC2}"/>
     <hyperlink ref="H7" r:id="rId4" location="G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D" xr:uid="{69B67A7E-F5DF-4731-9108-D2B26EA17B5F}"/>
-    <hyperlink ref="H8" r:id="rId5" xr:uid="{DBC01AE3-04B8-416B-9595-44BE25A3933E}"/>
+    <hyperlink ref="H8" r:id="rId5" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload" xr:uid="{DBC01AE3-04B8-416B-9595-44BE25A3933E}"/>
     <hyperlink ref="H10" r:id="rId6" xr:uid="{7487445C-39DC-478E-A0C1-51E26435126C}"/>
     <hyperlink ref="H11" r:id="rId7" xr:uid="{6CCC7B2B-D020-47F7-8043-90FE30930310}"/>
     <hyperlink ref="H12" r:id="rId8" xr:uid="{69D4528E-61E1-4387-8E6E-26DBAC7C4506}"/>
@@ -3276,16 +3276,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" ht="28.5">
+    <row r="6" spans="1:8" ht="85.5">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -3392,7 +3392,7 @@
       <c r="B7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="12" t="s">
         <v>228</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -3517,7 +3517,7 @@
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1rESYHt5o1iQarVEFVaAx0mJylvMq4XkD%26export%3Ddownload" xr:uid="{BC28DF17-63E6-47BC-BA78-B6935EDD0CDA}"/>
     <hyperlink ref="C5" r:id="rId2" location="G1WnnMAADEEE-IsjPr1TTquf-2JKCgalI1#%7B%22pageId%22%3A%220YesyBUdXUmlOLOw5Ugs%22%7D" xr:uid="{9F01BBAD-8F77-45FC-9D84-2003B71C6FD4}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{2AF1EAE9-F8D1-49EF-AF7D-566C521146B1}"/>
+    <hyperlink ref="C6" r:id="rId3" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Lxjyn7C33eKcqnTFqsEF9ZGF_tcGvsgr%26export%3Ddownload" xr:uid="{2AF1EAE9-F8D1-49EF-AF7D-566C521146B1}"/>
     <hyperlink ref="C7" r:id="rId4" location="Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" display="https://viewer.diagrams.net/?tags=%7B%7D&amp;lightbox=1&amp;highlight=0000ff&amp;edit=_blank&amp;layers=1&amp;nav=1&amp;title=Sequence%20Diagram%20-%20Overtime.drawio&amp;dark=auto#Uhttps%3A%2F%2Fdrive.google.com%2Fuc%3Fid%3D1Bkmql88aJhFnxKD1ADPUpkwqfoEABKN5%26export%3Ddownload" xr:uid="{AE6E4056-F5FA-416E-B7C3-AA75D0E1F713}"/>
     <hyperlink ref="C8" r:id="rId5" xr:uid="{DBB043FB-01CA-4628-BB08-82C86E442EF8}"/>
     <hyperlink ref="C9" r:id="rId6" xr:uid="{82B08C55-5769-410C-8DEB-7239FC87F6D9}"/>
@@ -3543,17 +3543,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4036,23 +4036,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="C3" s="17"/>
+      <c r="C3" s="18"/>
       <c r="E3" s="1" t="s">
         <v>123</v>
       </c>
@@ -4064,10 +4064,10 @@
       <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="17"/>
+      <c r="C4" s="18"/>
       <c r="E4" t="s">
         <v>125</v>
       </c>
@@ -4079,10 +4079,10 @@
       <c r="A5" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="18"/>
+      <c r="C5" s="19"/>
       <c r="E5" t="s">
         <v>127</v>
       </c>
@@ -4094,10 +4094,10 @@
       <c r="A6" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="17"/>
+      <c r="C6" s="18"/>
       <c r="E6" t="s">
         <v>129</v>
       </c>
@@ -4109,10 +4109,10 @@
       <c r="A7" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="17"/>
+      <c r="C7" s="18"/>
       <c r="E7" t="s">
         <v>131</v>
       </c>
@@ -4124,10 +4124,10 @@
       <c r="A8" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="17"/>
+      <c r="C8" s="18"/>
       <c r="E8" t="s">
         <v>133</v>
       </c>
@@ -4139,10 +4139,10 @@
       <c r="A9" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="C9" s="17"/>
+      <c r="C9" s="18"/>
       <c r="E9" t="s">
         <v>135</v>
       </c>
@@ -4154,10 +4154,10 @@
       <c r="A10" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C10" s="17"/>
+      <c r="C10" s="18"/>
       <c r="E10" t="s">
         <v>137</v>
       </c>
@@ -4169,10 +4169,10 @@
       <c r="A11" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C11" s="17"/>
+      <c r="C11" s="18"/>
       <c r="E11" t="s">
         <v>139</v>
       </c>
@@ -4222,16 +4222,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="B4" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -4255,42 +4255,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="9"/>
@@ -4301,32 +4301,32 @@
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
     </row>
     <row r="8" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" ht="42" customHeight="1">
       <c r="A10" s="5"/>
@@ -4337,124 +4337,119 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="15" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
     </row>
     <row r="17" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
     </row>
     <row r="19" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
     </row>
     <row r="20" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
     </row>
     <row r="21" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
     </row>
     <row r="23" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F9"/>
     <mergeCell ref="A20:F21"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F25"/>
@@ -4463,6 +4458,11 @@
     <mergeCell ref="A12:F13"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
